--- a/artfynd/A 17992-2025 artfynd.xlsx
+++ b/artfynd/A 17992-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120553313</v>
+        <v>120553312</v>
       </c>
       <c r="B2" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -768,11 +763,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>4 substratenheter # ordentligt gamla sälgar</t>
+          <t>1 substratenheter # ordentligt gammal sälg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120553312</v>
+        <v>120553313</v>
       </c>
       <c r="B3" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,11 +877,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # ordentligt gammal sälg</t>
+          <t>4 substratenheter # ordentligt gamla sälgar</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 17992-2025 artfynd.xlsx
+++ b/artfynd/A 17992-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553312</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553313</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>